--- a/output/结果汇总.xlsx
+++ b/output/结果汇总.xlsx
@@ -6819,7 +6819,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>mg/L(悬浮液)</t>
+          <t>mg/g</t>
         </is>
       </c>
     </row>
